--- a/artfynd/A 9129-2024 artfynd.xlsx
+++ b/artfynd/A 9129-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1201,6 +1201,120 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115111709</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90283</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 9129, Aveslätt, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>586962</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6406254</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9129-2024 artfynd.xlsx
+++ b/artfynd/A 9129-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1315,6 +1315,679 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115142168</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104645</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 9129. Aveslätt, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>586985</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6406231</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115142228</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 9129, Aveslätt, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>586974</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6406245</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115142120</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 9129, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>586987</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6406225</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115142211</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 9129, Aveslätt, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>586983</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6406242</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>115142297</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91549</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 9129, Aveslätt, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>586898</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6406323</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115142190</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 9129, Aveslätt, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>586996</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6406231</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
